--- a/output/graficos_dimensiones/comunal_e_preneta_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2019_biobio.xlsx
@@ -129,12 +129,12 @@
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:48</t>
+    <t xml:space="preserve">2026-09-09 23:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1101,7 +1101,7 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8305</v>
+        <v>8102</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1114,7 +1114,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8102</v>
+        <v>8305</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_preneta_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:49</t>
+    <t xml:space="preserve">2026-09-18 10:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
